--- a/BA/Part 1_Stakeholder Analysis amp Management-20260912/Artifacts/4. Communication Plan_VNS.xlsx
+++ b/BA/Part 1_Stakeholder Analysis amp Management-20260912/Artifacts/4. Communication Plan_VNS.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Communication_Plan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Communication_Plan'!$B$8:$G$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Communication_Plan'!$B$8:$G$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G39"/>
+  <dimension ref="B2:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -919,118 +919,118 @@
     <row r="17" ht="46" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Team Retrospective</t>
+          <t>Increment Demo for the Customer</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Demo + working meeting</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Every two weeks, Friday</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Identify what works and what does not, and agree concrete process improvements for the next two weeks</t>
+          <t>Show the working increment, confirm that it matches the requirements and collect corrections</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Project Manager (N. Zankovych)</t>
+          <t>Product Owner (K. Holovskyi)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Whole project team</t>
+          <t>Nataliia Boiko, PO, PM, BA, QA</t>
         </is>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1">
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Increment Demo for the Customer</t>
+          <t>Team Retrospective</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Demo + working meeting</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Every two weeks, Friday</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Show the working increment, confirm that it matches the requirements and collect corrections</t>
+          <t>Identify what works and what does not, and agree concrete process improvements for the next two weeks</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Product Owner (K. Holovskyi)</t>
+          <t>Project Manager (N. Zankovych)</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Nataliia Boiko, PO, PM, BA, QA</t>
+          <t>Whole project team</t>
         </is>
       </c>
     </row>
     <row r="19" ht="46" customHeight="1">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Summary for the Rector's Office</t>
+          <t>Change Management Meeting</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>E-mail with a one-page summary</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Once per semester and at control points</t>
+          <t>As needed, within 2 business days of a request</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Report status, pilot results and the decision needed on scaling the product across the university</t>
+          <t>Review a scope change request, assess the impact on the schedule and take a decision</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Project Manager (N. Zankovych)</t>
+          <t>Product Owner (K. Holovskyi)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Nataliia Shakhovska (Rector), Lviv Polytechnic National University, PM</t>
+          <t>PO, PM, BA, Tech Lead; Nataliia Boiko for material changes</t>
         </is>
       </c>
     </row>
     <row r="20" ht="46" customHeight="1">
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Reporting to the Ministry of Education and Science</t>
+          <t>Summary for the Rector's Office</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Official report</t>
+          <t>E-mail with a one-page summary</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Once per semester</t>
+          <t>Once per semester and at control points</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Inform the regulator about the course and results of the project and its compliance with regulatory requirements</t>
+          <t>Report status, pilot results and the decision needed on scaling the product across the university</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -1040,364 +1040,236 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Ministry of Education and Science of Ukraine, Lviv Polytechnic National University, Rector, PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="46" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>LLM API Cost and Quota Review</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>E-mail + support ticket</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Monthly and on tariff changes</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Control the cost of the AI module, the daily request limits per user and the data processing terms</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Project Manager (N. Zankovych)</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>PM, Tech Lead, DevOps, Lviv Polytechnic National University</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="46" customHeight="1">
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Change Management Meeting</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Meeting</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>As needed, within 2 business days of a request</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Review a scope change request, assess the impact on the schedule and take a decision</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Product Owner (K. Holovskyi)</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>PO, PM, BA, Tech Lead; Nataliia Boiko for material changes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="46" customHeight="1">
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Pilot Announcement to End Users</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Announcement in learning channels</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Before the pilot and monthly thereafter</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Recruit pilot participants, explain the value of the product and collect sign-ups</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Product Owner (K. Holovskyi)</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>End users — Lviv Polytechnic students, PO, PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="46" customHeight="1">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Project Handover and Closure</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Meeting + documentation package</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Once, at the end of the project</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Hand over the system, documentation and lessons learned to the customer and sign the acceptance record</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Project Manager (N. Zankovych)</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Lviv Polytechnic National University, Nataliia Boiko, Technical Department, whole team</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="6" t="inlineStr">
+          <t>Nataliia Shakhovska (Rector), Lviv Polytechnic National University, PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>COMMUNICATION ESCALATION PROCESS</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="7" t="inlineStr">
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>Decision Authority</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>Timeframe for Resolution</t>
         </is>
       </c>
-      <c r="G27" s="8" t="n"/>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="B28" s="9" t="inlineStr">
+      <c r="G23" s="8" t="n"/>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Priority 1</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Major impact: the team is blocked, or the pilot or project deadline is at risk</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Lviv Polytechnic National University (Sponsor)</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Within 1 business day</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="B29" s="9" t="inlineStr">
+    <row r="25" ht="32" customHeight="1">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Priority 2</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Medium impact: individual activities or the MVP scope may slip</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Product Owner</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Within 2 business days</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="B30" s="9" t="inlineStr">
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Priority 3</t>
         </is>
       </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Slight impact: minor scheduling difficulties with no effect on scope or outcome</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Within 3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Priority 4</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>No impact on the project, but a better solution may exist</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Handled through the change management process</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>COMMUNICATION STANDARDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Meeting agenda</t>
+        </is>
+      </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Slight impact: minor scheduling difficulties with no effect on scope or outcome</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Within 3 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>Priority 4</t>
+          <t>Distributed to participants no later than 2 business days before the meeting; identifies the topics, the presenter and a time limit for each. The first item is always a review of action items from the previous meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Meeting minutes</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>No impact on the project, but a better solution may exist</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Handled through the change management process</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>COMMUNICATION STANDARDS</t>
+          <t>Published within 1 business day after the meeting; contain the decisions taken, new action items with a named owner and due date, and the Parking Lot list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Channels</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Formal documents and approvals — university @lpnu.ua mailboxes. Day-to-day team work — team chat. Tasks and defects — issue tracker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Confidentiality</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Personal data of students and lecturers is not distributed through external channels. Any transfer of course materials to the external LLM API is approved by Lviv Polytechnic National University as the owner of the data.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Meeting agenda</t>
+          <t>Escalation rule</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Distributed to participants no later than 2 business days before the meeting; identifies the topics, the presenter and a time limit for each. The first item is always a review of action items from the previous meeting.</t>
+          <t>Issues involving personal data or the transfer of materials to the external LLM API are escalated to the sponsor regardless of the priority assigned.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Meeting minutes</t>
+          <t>Link to the register</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Published within 1 business day after the meeting; contain the decisions taken, new action items with a named owner and due date, and the Parking Lot list.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>Channels</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Formal documents and approvals — university @lpnu.ua mailboxes. Day-to-day team work — team chat. Tasks and defects — issue tracker.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>Confidentiality</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Personal data of students and lecturers is not distributed through external channels. Any transfer of course materials to the external LLM API is approved by Lviv Polytechnic National University as the owner of the data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>Escalation rule</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Issues involving personal data or the transfer of materials to the external LLM API are escalated to the sponsor regardless of the priority assigned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>Link to the register</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
           <t>The frequency and method of each communication match the “Preferable way of communication” and “Frequency of Communication” columns in “1. Stakeholder Register_VNS.xlsx”.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B8:G24"/>
+  <autoFilter ref="B8:G20"/>
   <mergeCells count="25">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="F4:G4"/>
+    <mergeCell ref="C30:G30"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="C34:G34"/>
-    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F25:G25"/>
     <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C33:G33"/>
     <mergeCell ref="F6:G6"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="B29:G29"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="F5:G5"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="F26:G26"/>
     <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="F23:G23"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="C32:G32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/BA/Part 1_Stakeholder Analysis amp Management-20260912/Artifacts/4. Communication Plan_VNS.xlsx
+++ b/BA/Part 1_Stakeholder Analysis amp Management-20260912/Artifacts/4. Communication Plan_VNS.xlsx
@@ -547,12 +547,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="66" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="76" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="2" ht="26" customHeight="1">
@@ -660,7 +660,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="46" customHeight="1">
+    <row r="9" ht="52" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Team Standup</t>
@@ -692,7 +692,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="46" customHeight="1">
+    <row r="10" ht="52" customHeight="1">
       <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Weekly Planning and Backlog Review</t>
@@ -724,7 +724,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="46" customHeight="1">
+    <row r="11" ht="52" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Requirements Elicitation Meeting with the Customer</t>
@@ -756,7 +756,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="46" customHeight="1">
+    <row r="12" ht="52" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
         <is>
           <t>End-user Feedback Session</t>
@@ -788,7 +788,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="46" customHeight="1">
+    <row r="13" ht="52" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Technical Sync</t>
@@ -820,7 +820,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="46" customHeight="1">
+    <row r="14" ht="52" customHeight="1">
       <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Quality and Defect Report</t>
@@ -852,7 +852,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="46" customHeight="1">
+    <row r="15" ht="52" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Coordination with the University Technical Department</t>
@@ -884,7 +884,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="46" customHeight="1">
+    <row r="16" ht="52" customHeight="1">
       <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Status Report to the Sponsor</t>
@@ -916,7 +916,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="46" customHeight="1">
+    <row r="17" ht="52" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Increment Demo for the Customer</t>
@@ -948,7 +948,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="46" customHeight="1">
+    <row r="18" ht="52" customHeight="1">
       <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Team Retrospective</t>
@@ -980,7 +980,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="46" customHeight="1">
+    <row r="19" ht="52" customHeight="1">
       <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Change Management Meeting</t>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="46" customHeight="1">
+    <row r="20" ht="52" customHeight="1">
       <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Summary for the Rector's Office</t>
